--- a/붙임2. SW제품 테스트 결과보고서(작성본).xlsx
+++ b/붙임2. SW제품 테스트 결과보고서(작성본).xlsx
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.88671875" customWidth="1" style="11" min="1" max="1"/>
@@ -1327,39 +1327,40 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customFormat="1" customHeight="1" s="10">
+    <row r="4" ht="66" customFormat="1" customHeight="1" s="10">
       <c r="A4" s="52" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>업로드</t>
         </is>
       </c>
       <c r="C4" s="52" t="inlineStr">
         <is>
-          <t>인가·정보노출</t>
+          <t>데이터 무결성</t>
         </is>
       </c>
       <c r="D4" s="52" t="inlineStr">
         <is>
-          <t>미게시 콘텐츠 접근제어</t>
+          <t>배치 업로드 원자성</t>
         </is>
       </c>
       <c r="E4" s="53" t="inlineStr">
         <is>
-          <t>1. active=false(미게시) 스페이스에 씬 생성
-2. 로그인 토큰 없이 GET /vt?VT=&lt;7자리 hex&gt; 호출</t>
+          <t>[오류주입·상태전이]
+1. 편집 모드에서 파노라마 여러 장 + 미지원 포맷(webp) 1장을 한 번에 다중선택 업로드
+2. 업로드 결과·카테고리 목록 확인</t>
         </is>
       </c>
       <c r="F4" s="53" t="inlineStr">
         <is>
-          <t>미인증 요청은 401로 차단되고 미게시 콘텐츠 메타데이터는 노출되지 않아야 함</t>
+          <t>미지원 1장만 거부되고 정상 파일은 개별 등록(부분 성공)</t>
         </is>
       </c>
       <c r="G4" s="53" t="inlineStr">
         <is>
-          <t>HTTP 200으로 스페이스 제목·씬 정보·360 타일 경로·원본 파일명 등 메타데이터 반환(인증 게이팅 부재). 미게시 썸네일도 비로그인 노출(N-3). 단 원본 타일 본체는 서명URL 403으로 보호됨</t>
+          <t>같은 배치의 정상 파노라마까지 전량 등록 실패(데이터 손실). 실패 사유 안내 없이 빈 유령 카테고리만 잔존. 8종 통제실험(콘텐츠·용량·개수·순서 교란 제거)에서 거부파일 포함 시 재현율 100%. API상 정상 씬은 서버에 유지 → 클라이언트 배치 완료 핸들러 원인 시사</t>
         </is>
       </c>
       <c r="H4" s="52" t="inlineStr">
@@ -1374,42 +1375,45 @@
       </c>
       <c r="J4" s="52" t="inlineStr">
         <is>
-          <t>A-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customFormat="1" customHeight="1" s="10">
+          <t>E-018</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="66" customFormat="1" customHeight="1" s="10">
       <c r="A5" s="52" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t>업로드</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C5" s="52" t="inlineStr">
         <is>
-          <t>데이터 무결성</t>
+          <t>인가 기능 실패</t>
         </is>
       </c>
       <c r="D5" s="52" t="inlineStr">
         <is>
-          <t>배치 업로드 원자성</t>
+          <t>미게시 콘텐츠 접근제어</t>
         </is>
       </c>
       <c r="E5" s="53" t="inlineStr">
         <is>
-          <t>1. 다중선택 배치 업로드에 미지원 포맷(webp) 1장 + 정상 파노라마 여러 장을 함께 업로드</t>
+          <t>[오류주입(부정)·경험기반]
+1. active=false(미게시) 스페이스에 씬 생성
+2. 로그인 토큰 없이(비인증) GET /vt?VT=&lt;7자리 hex&gt; 호출
+3. 시크릿탭에서 썸네일 URL 직접 열기</t>
         </is>
       </c>
       <c r="F5" s="53" t="inlineStr">
         <is>
-          <t>미지원 1장만 거부되고 정상 파일은 개별 등록되어야 함(부분 성공)</t>
+          <t>인가 기능이 동작하여 미인증 요청은 401 차단, 미게시 콘텐츠·썸네일 비노출</t>
         </is>
       </c>
       <c r="G5" s="53" t="inlineStr">
         <is>
-          <t>같은 배치의 정상 파노라마까지 전량 등록 실패(데이터 손실). 실패 사유 안내 없이 빈 유령 카테고리만 잔존. 8종 통제실험에서 거부파일 포함 시 재현율 100%. 서버엔 정상 씬 유지 확인 → 클라이언트 배치 핸들러 원인 시사</t>
+          <t>인가 기능이 동작하지 않아 HTTP 200으로 제목·씬·360타일 경로·원본 파일명 반환. 미게시 썸네일도 비로그인 노출(N-3 체인). 원본 타일 본체만 서명URL 403으로 보호</t>
         </is>
       </c>
       <c r="H5" s="52" t="inlineStr">
@@ -1424,42 +1428,43 @@
       </c>
       <c r="J5" s="52" t="inlineStr">
         <is>
-          <t>E-018</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customFormat="1" customHeight="1" s="10">
+          <t>A-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customFormat="1" customHeight="1" s="10">
       <c r="A6" s="52" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>업로드</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>인증</t>
+          <t>업로드 처리</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>로그인 사용자 열거</t>
+          <t>해상도 경계</t>
         </is>
       </c>
       <c r="E6" s="53" t="inlineStr">
         <is>
-          <t>1. 없는 계정 / 가입계정+틀린비번으로 각각 POST /user/login</t>
+          <t>[경계값·A/B 통제]
+1. 동일 2:1 유효 JPEG를 해상도만 바꿔 A/B 업로드(약 10771×5385 vs 7180×3590 vs 11968×5984)</t>
         </is>
       </c>
       <c r="F6" s="53" t="inlineStr">
         <is>
-          <t>실패는 401 + 계정 존재를 숨기는 단일 일반 메시지</t>
+          <t>유효 규격이면 해상도와 무관하게 정상 등록</t>
         </is>
       </c>
       <c r="G6" s="53" t="inlineStr">
         <is>
-          <t>없는 계정 → HTTP 201 {code:101,"id not exist"}, 가입계정+오답 → HTTP 201 {code:102,"pwd not compare"}. 코드로 계정 존재 여부 구분(사용자 열거) + 인증 실패를 2xx로 통보</t>
+          <t>약 10771×5385는 jobId 발급 후 씬 미등록(기능 실패), 7180×3590·11968×5984는 통과. 해상도만 스왑해도 성패 반전(콘텐츠 무관). 실패 사유 안내 없음</t>
         </is>
       </c>
       <c r="H6" s="52" t="inlineStr">
@@ -1474,43 +1479,44 @@
       </c>
       <c r="J6" s="52" t="inlineStr">
         <is>
-          <t>A-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customFormat="1" customHeight="1" s="10">
+          <t>E-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customFormat="1" customHeight="1" s="10">
       <c r="A7" s="52" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>업로드</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>입력검증</t>
+          <t>업로드 검증</t>
         </is>
       </c>
       <c r="D7" s="52" t="inlineStr">
         <is>
-          <t>예외 처리</t>
+          <t>최소 해상도</t>
         </is>
       </c>
       <c r="E7" s="53" t="inlineStr">
         <is>
-          <t>1. 초장문 파일명(한글 100자+) 이미지 업로드
-2. PUT /content에 불완전 body 전송</t>
+          <t>[경계값]
+1. 초소형(100×50) 이미지를 360 씬으로 업로드
+2. 뷰어에서 렌더 확인</t>
         </is>
       </c>
       <c r="F7" s="53" t="inlineStr">
         <is>
-          <t>잘못된 입력은 4xx(400)로 안내</t>
+          <t>최소 해상도/비율 미달은 거부 또는 안내</t>
         </is>
       </c>
       <c r="G7" s="53" t="inlineStr">
         <is>
-          <t>POST /scene/autoNorth → 500, PUT /content → 500 (POST /content 생성은 400 검증 존재 → 검증 비대칭). 500 본문 스택 미노출은 양호</t>
+          <t>초소형 씬이 그대로 통과되어 뷰어 완전 검은 화면. 최소 크기·비율 검증 부재, 안내·플레이스홀더 없음(기능 부정확)</t>
         </is>
       </c>
       <c r="H7" s="52" t="inlineStr">
@@ -1525,43 +1531,45 @@
       </c>
       <c r="J7" s="52" t="inlineStr">
         <is>
-          <t>A-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customFormat="1" customHeight="1" s="10">
+          <t>E-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customFormat="1" customHeight="1" s="10">
       <c r="A8" s="52" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>UI/기능</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>보안설정</t>
+          <t>상태 동기화</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>응답 헤더·토큰 저장</t>
+          <t>업로드 후 갱신</t>
         </is>
       </c>
       <c r="E8" s="53" t="inlineStr">
         <is>
-          <t>1. roundpic.io / vtapi 응답 헤더 확인
-2. 로그인 후 localStorage 확인</t>
+          <t>[상태전이]
+1. 씬 업로드 성공 토스트 확인
+2. 즉시 에디터 씬 목록 확인
+3. 새로고침 후 재확인</t>
         </is>
       </c>
       <c r="F8" s="53" t="inlineStr">
         <is>
-          <t>CSP·X-Frame-Options·HSTS 등 표준 보안 헤더 존재, 토큰 안전 저장</t>
+          <t>업로드 완료 후 씬이 즉시 화면에 표시</t>
         </is>
       </c>
       <c r="G8" s="53" t="inlineStr">
         <is>
-          <t>보안 헤더 6종(CSP·X-Frame-Options·HSTS·X-Content-Type-Options·Referrer-Policy·Permissions-Policy) 전무 + x-powered-by:Express 노출. accessToken·refreshToken이 localStorage 평문 저장</t>
+          <t>업로드 성공 토스트에도 에디터가 "이미지 없음"으로 오표시, 새로고침해야 반영(상태 미동기화). 사용자가 중복 업로드할 소지</t>
         </is>
       </c>
       <c r="H8" s="52" t="inlineStr">
@@ -1576,11 +1584,11 @@
       </c>
       <c r="J8" s="52" t="inlineStr">
         <is>
-          <t>A-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customFormat="1" customHeight="1" s="10">
+          <t>E-012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customFormat="1" customHeight="1" s="10">
       <c r="A9" s="52" t="n">
         <v>6</v>
       </c>
@@ -1591,27 +1599,29 @@
       </c>
       <c r="C9" s="52" t="inlineStr">
         <is>
-          <t>업로드 처리</t>
+          <t>업로드 안내</t>
         </is>
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>해상도 검증</t>
+          <t>용량 상한</t>
         </is>
       </c>
       <c r="E9" s="53" t="inlineStr">
         <is>
-          <t>1. 동일 2:1 유효 JPEG를 해상도만 바꿔 A/B 업로드(약 10771×5385 vs 7180×3590)</t>
+          <t>[경계값]
+1. 안내 문구 확인
+2. 24MB, 30MB, 35MB 파노라마를 이진탐색으로 업로드</t>
         </is>
       </c>
       <c r="F9" s="53" t="inlineStr">
         <is>
-          <t>유효 규격이면 해상도 무관하게 정상 등록</t>
+          <t>안내된 상한과 실제 처리 상한 일치</t>
         </is>
       </c>
       <c r="G9" s="53" t="inlineStr">
         <is>
-          <t>약 10771×5385는 jobId 발급 후 씬 미등록(실패), 7180×3590·11968×5984는 통과. 해상도만 스왑해도 성패 반전(콘텐츠 무관). 실패 사유 안내 없음</t>
+          <t>안내 "5MB까지"인데 실측 24MB 통과 / 35MB 거부. 상한 미정의·안내와 5배 이상 불일치(수행결과≠예상결과)</t>
         </is>
       </c>
       <c r="H9" s="52" t="inlineStr">
@@ -1626,42 +1636,44 @@
       </c>
       <c r="J9" s="52" t="inlineStr">
         <is>
-          <t>E-019</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customFormat="1" customHeight="1" s="10">
+          <t>E-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customFormat="1" customHeight="1" s="10">
       <c r="A10" s="52" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>업로드</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
         <is>
-          <t>업로드·입력검증</t>
+          <t>인증</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>최소 크기 검증</t>
+          <t>로그인 사용자 열거</t>
         </is>
       </c>
       <c r="E10" s="53" t="inlineStr">
         <is>
-          <t>1. 초소형(100×50) 이미지를 360 씬으로 업로드 후 뷰어 확인</t>
+          <t>[결정표·오류주입]
+1. 없는 계정 / 가입계정+틀린비번 각각 POST /user/login
+2. 응답 코드·메시지 대조</t>
         </is>
       </c>
       <c r="F10" s="53" t="inlineStr">
         <is>
-          <t>최소 해상도/비율 미달은 거부 또는 안내</t>
+          <t>실패는 401 + 계정 존재를 숨기는 단일 일반 메시지</t>
         </is>
       </c>
       <c r="G10" s="53" t="inlineStr">
         <is>
-          <t>초소형 씬이 그대로 통과되어 뷰어 완전 검은 화면. 최소 크기·비율 검증 부재, 안내·플레이스홀더 없음</t>
+          <t>없는 계정 → HTTP 201 {code:101,"id not exist"}, 가입계정+오답 → HTTP 201 {code:102,"pwd not compare"}. 코드로 계정 존재 여부 구분(사용자 열거) + 인증 실패를 2xx로 통보(부정확 동작)</t>
         </is>
       </c>
       <c r="H10" s="52" t="inlineStr">
@@ -1676,42 +1688,44 @@
       </c>
       <c r="J10" s="52" t="inlineStr">
         <is>
-          <t>E-009</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customFormat="1" customHeight="1" s="10">
+          <t>A-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customFormat="1" customHeight="1" s="10">
       <c r="A11" s="52" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>업로드</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>업로드 안내</t>
+          <t>예외 처리</t>
         </is>
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>용량 상한</t>
+          <t>서버 500</t>
         </is>
       </c>
       <c r="E11" s="53" t="inlineStr">
         <is>
-          <t>1. 안내 문구 확인 후 용량별 파노라마 업로드(24MB, 35MB)</t>
+          <t>[경계값·오류주입]
+1. 초장문 파일명(한글 100자+) 이미지 업로드
+2. PUT /content에 불완전 body 전송</t>
         </is>
       </c>
       <c r="F11" s="53" t="inlineStr">
         <is>
-          <t>안내된 상한과 실제 처리 상한 일치</t>
+          <t>잘못된 입력은 4xx(400)로 안내</t>
         </is>
       </c>
       <c r="G11" s="53" t="inlineStr">
         <is>
-          <t>안내 "5MB까지"인데 실측 24MB 통과 / 35MB 거부. 상한 미정의·안내와 5배 이상 불일치</t>
+          <t>POST /scene/autoNorth → 500, PUT /content → 500(생성 POST /content는 400 검증 존재 → 검증 비대칭). 서버가 비정상 응답(500). 스택 미노출은 양호</t>
         </is>
       </c>
       <c r="H11" s="52" t="inlineStr">
@@ -1726,42 +1740,44 @@
       </c>
       <c r="J11" s="52" t="inlineStr">
         <is>
-          <t>E-010</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customFormat="1" customHeight="1" s="10">
+          <t>A-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="66" customFormat="1" customHeight="1" s="10">
       <c r="A12" s="52" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>상태 표시</t>
+          <t>보안 설정</t>
         </is>
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>업로드 후 갱신</t>
+          <t>응답 헤더·토큰</t>
         </is>
       </c>
       <c r="E12" s="53" t="inlineStr">
         <is>
-          <t>1. 씬 업로드 직후 에디터 화면 확인</t>
+          <t>[보안 테스트]
+1. roundpic.io / vtapi 응답 헤더 확인
+2. 로그인 후 localStorage 확인</t>
         </is>
       </c>
       <c r="F12" s="53" t="inlineStr">
         <is>
-          <t>업로드 완료 후 씬이 즉시 표시</t>
+          <t>CSP·X-Frame-Options·HSTS 등 표준 보안 헤더 존재, 토큰 안전 저장</t>
         </is>
       </c>
       <c r="G12" s="53" t="inlineStr">
         <is>
-          <t>업로드 직후 "이미지 없음"으로 오표시, 새로고침해야 반영(비동기 job 반영 지연). 중복 업로드 유발 소지</t>
+          <t>보안 헤더 6종(CSP·X-Frame-Options·HSTS·X-Content-Type-Options·Referrer-Policy·Permissions-Policy) 전무 + x-powered-by:Express 노출. accessToken·refreshToken localStorage 평문 → XSS 시 세션 탈취 표면 확대</t>
         </is>
       </c>
       <c r="H12" s="52" t="inlineStr">
@@ -1776,43 +1792,43 @@
       </c>
       <c r="J12" s="52" t="inlineStr">
         <is>
-          <t>E-012</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1" s="47">
+          <t>A-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1" s="47">
       <c r="A13" s="52" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>업로드</t>
         </is>
       </c>
       <c r="C13" s="52" t="inlineStr">
         <is>
-          <t>입력검증</t>
+          <t>포맷 검증</t>
         </is>
       </c>
       <c r="D13" s="52" t="inlineStr">
         <is>
-          <t>서버측 새니타이즈</t>
+          <t>매직바이트 우회</t>
         </is>
       </c>
       <c r="E13" s="53" t="inlineStr">
         <is>
-          <t>1. 회사명에 &lt;b&gt;·&lt;svg onload&gt; 등 삽입 저장
-2. 대시보드에서 렌더 확인</t>
+          <t>[오류주입(위장)]
+1. 실제 webp 바이트를 .jpg + Content-Type image/jpeg로 위장 업로드</t>
         </is>
       </c>
       <c r="F13" s="53" t="inlineStr">
         <is>
-          <t>특수문자 이스케이프/새니타이즈</t>
+          <t>실제 콘텐츠(매직바이트) 기반 포맷 검증</t>
         </is>
       </c>
       <c r="G13" s="53" t="inlineStr">
         <is>
-          <t>서버가 미이스케이프 원문 저장(미새니타이즈). 단 Angular 렌더가 자동 이스케이프하여 실행은 방어됨 → 저장형 XSS 아님으로 하향. 공개 뷰어가 innerHTML 계열이면 재평가 필요</t>
+          <t>게이트가 확장자/MIME만 신뢰 → 위장 파일 202 통과(jobId 발급). 진짜 webp(code203)와 대비. 저장소 비인증 403이라 즉시 실행 표면은 제한적</t>
         </is>
       </c>
       <c r="H13" s="52" t="inlineStr">
@@ -1827,11 +1843,11 @@
       </c>
       <c r="J13" s="52" t="inlineStr">
         <is>
-          <t>N-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1" s="47">
+          <t>N-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1" s="47">
       <c r="A14" s="52" t="n">
         <v>11</v>
       </c>
@@ -1842,27 +1858,28 @@
       </c>
       <c r="C14" s="52" t="inlineStr">
         <is>
-          <t>업로드 검증</t>
+          <t>상태코드 정합성</t>
         </is>
       </c>
       <c r="D14" s="52" t="inlineStr">
         <is>
-          <t>포맷 게이트 우회</t>
+          <t>거부 통보</t>
         </is>
       </c>
       <c r="E14" s="53" t="inlineStr">
         <is>
-          <t>1. 실제 webp 바이트를 .jpg + Content-Type image/jpeg로 위장 업로드</t>
+          <t>[동등분할]
+1. webp/bmp 업로드 시 HTTP 상태·코드 확인</t>
         </is>
       </c>
       <c r="F14" s="53" t="inlineStr">
         <is>
-          <t>실제 콘텐츠(매직바이트) 기반 포맷 검증</t>
+          <t>거부는 4xx 또는 적절한 코드로 통보</t>
         </is>
       </c>
       <c r="G14" s="53" t="inlineStr">
         <is>
-          <t>게이트가 확장자/MIME만 신뢰 → 위장 파일 202 통과(jobId 발급). 진짜 webp(code203)와 대비. 저장소는 비인증 403이라 즉시 실행 표면은 제한적</t>
+          <t>업로드 거부(code203)를 HTTP 202로 통보(webp/bmp). 성공/거부가 같은 상태코드 → 시맨틱 불일치</t>
         </is>
       </c>
       <c r="H14" s="52" t="inlineStr">
@@ -1877,42 +1894,43 @@
       </c>
       <c r="J14" s="52" t="inlineStr">
         <is>
-          <t>N-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1" s="47">
+          <t>A-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1" s="47">
       <c r="A15" s="52" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>업로드</t>
         </is>
       </c>
       <c r="C15" s="52" t="inlineStr">
         <is>
-          <t>인가·정보노출</t>
+          <t>실패 통보</t>
         </is>
       </c>
       <c r="D15" s="52" t="inlineStr">
         <is>
-          <t>썸네일 접근제어</t>
+          <t>무효파일 폐기</t>
         </is>
       </c>
       <c r="E15" s="53" t="inlineStr">
         <is>
-          <t>1. 시크릿탭(비로그인)에서 미게시 스페이스 썸네일 URL 직접 열기</t>
+          <t>[오류주입]
+1. 0바이트·손상 파일 업로드 후 비동기 처리 결과 확인</t>
         </is>
       </c>
       <c r="F15" s="53" t="inlineStr">
         <is>
-          <t>미게시 콘텐츠 썸네일은 인증 필요</t>
+          <t>무효 파일은 실패 사유 통보</t>
         </is>
       </c>
       <c r="G15" s="53" t="inlineStr">
         <is>
-          <t>미게시(토글 OFF) 스페이스 썸네일(thumbSquare.jpg 240×240)이 비로그인으로 그대로 로드됨(A-01 확장 체인). 원본 타일 본체는 403 보호</t>
+          <t>게이트 202 수락 후 무효 파일을 비동기 단계에서 조용히 폐기(에러 통보 부재)</t>
         </is>
       </c>
       <c r="H15" s="52" t="inlineStr">
@@ -1927,42 +1945,43 @@
       </c>
       <c r="J15" s="52" t="inlineStr">
         <is>
-          <t>N-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1" s="47">
+          <t>A-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1" s="47">
       <c r="A16" s="52" t="n">
         <v>13</v>
       </c>
       <c r="B16" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>업로드</t>
         </is>
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>보안설정</t>
+          <t>포맷 정책</t>
         </is>
       </c>
       <c r="D16" s="52" t="inlineStr">
         <is>
-          <t>CORS 정책</t>
+          <t>gif 처리</t>
         </is>
       </c>
       <c r="E16" s="53" t="inlineStr">
         <is>
-          <t>1. API 응답의 CORS 헤더 확인</t>
+          <t>[동등분할]
+1. gif 업로드 후 게이트·비동기 결과 확인</t>
         </is>
       </c>
       <c r="F16" s="53" t="inlineStr">
         <is>
-          <t>명시적 오리진 화이트리스트</t>
+          <t>지원/미지원 정책 일관</t>
         </is>
       </c>
       <c r="G16" s="53" t="inlineStr">
         <is>
-          <t>Access-Control-Allow-Origin: * (와일드카드). Access-Control-Allow-Credentials 없어 즉각적 세션 탈취는 완화되나 화이트리스트 권장</t>
+          <t>gif가 게이트 202 수락되나 비동기 단계에서 거부(게이트-처리 불일치)</t>
         </is>
       </c>
       <c r="H16" s="52" t="inlineStr">
@@ -1977,42 +1996,43 @@
       </c>
       <c r="J16" s="52" t="inlineStr">
         <is>
-          <t>N-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1" s="47">
+          <t>A-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1" s="47">
       <c r="A17" s="52" t="n">
         <v>14</v>
       </c>
       <c r="B17" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>업로드</t>
         </is>
       </c>
       <c r="C17" s="52" t="inlineStr">
         <is>
-          <t>보안설정</t>
+          <t>포맷 정책</t>
         </is>
       </c>
       <c r="D17" s="52" t="inlineStr">
         <is>
-          <t>토큰 저장</t>
+          <t>accept 불일치</t>
         </is>
       </c>
       <c r="E17" s="53" t="inlineStr">
         <is>
-          <t>1. 로그인 후 localStorage 확인</t>
+          <t>[동등분할]
+1. 업로드 input의 accept 값과 실제 처리 포맷 대조</t>
         </is>
       </c>
       <c r="F17" s="53" t="inlineStr">
         <is>
-          <t>리프레시 토큰 안전 저장(httpOnly 등)</t>
+          <t>accept와 실제 처리 정책 일치</t>
         </is>
       </c>
       <c r="G17" s="53" t="inlineStr">
         <is>
-          <t>refreshToken이 localStorage 평문 저장(A-04 확장). 장기 세션 탈취 표면 확대</t>
+          <t>accept="image/*"인데 실제는 JPEG/PNG만 처리(webp 거부, gif 게이트 통과 후 거부). affordance-처리 불일치</t>
         </is>
       </c>
       <c r="H17" s="52" t="inlineStr">
@@ -2027,42 +2047,44 @@
       </c>
       <c r="J17" s="52" t="inlineStr">
         <is>
-          <t>N-5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1" s="47">
+          <t>E-020</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1" s="47">
       <c r="A18" s="52" t="n">
         <v>15</v>
       </c>
       <c r="B18" s="52" t="inlineStr">
         <is>
-          <t>업로드</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>업로드·시맨틱</t>
+          <t>입력검증</t>
         </is>
       </c>
       <c r="D18" s="52" t="inlineStr">
         <is>
-          <t>상태코드 정합성</t>
+          <t>서버측 새니타이즈</t>
         </is>
       </c>
       <c r="E18" s="53" t="inlineStr">
         <is>
-          <t>1. webp/bmp 파일 업로드 시 응답 확인</t>
+          <t>[오류주입(XSS)]
+1. 회사명에 &lt;b&gt;·&lt;svg onload&gt; 삽입 저장
+2. 대시보드에서 렌더 확인</t>
         </is>
       </c>
       <c r="F18" s="53" t="inlineStr">
         <is>
-          <t>거부는 4xx/적절한 코드로 통보</t>
+          <t>특수문자 이스케이프/새니타이즈</t>
         </is>
       </c>
       <c r="G18" s="53" t="inlineStr">
         <is>
-          <t>업로드 거부(code203)를 HTTP 202로 통보(webp/bmp). 성공/거부가 같은 상태코드 → 시맨틱 불일치 (과거 V2 증거, 이번 미재확인)</t>
+          <t>서버가 미이스케이프 원문 저장. 단 Angular 렌더가 자동 이스케이프하여 실행 방어됨 → 저장형 XSS 아님으로 하향. 공개 뷰어가 innerHTML 계열이면 재평가 필요</t>
         </is>
       </c>
       <c r="H18" s="52" t="inlineStr">
@@ -2077,42 +2099,43 @@
       </c>
       <c r="J18" s="52" t="inlineStr">
         <is>
-          <t>A-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1" s="47">
+          <t>N-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1" s="47">
       <c r="A19" s="52" t="n">
         <v>16</v>
       </c>
       <c r="B19" s="52" t="inlineStr">
         <is>
-          <t>업로드</t>
+          <t>입력검증</t>
         </is>
       </c>
       <c r="C19" s="52" t="inlineStr">
         <is>
-          <t>업로드 처리</t>
+          <t>형식 검증</t>
         </is>
       </c>
       <c r="D19" s="52" t="inlineStr">
         <is>
-          <t>실패 통보</t>
+          <t>URL</t>
         </is>
       </c>
       <c r="E19" s="53" t="inlineStr">
         <is>
-          <t>1. 무효 파일 업로드 후 비동기 처리 결과 확인</t>
+          <t>[동등분할]
+1. 스페이스 홍보링크(website)에 URL 아닌 문자열 입력·저장</t>
         </is>
       </c>
       <c r="F19" s="53" t="inlineStr">
         <is>
-          <t>무효 파일은 실패 사유 통보</t>
+          <t>URL 형식 검증·거부</t>
         </is>
       </c>
       <c r="G19" s="53" t="inlineStr">
         <is>
-          <t>게이트 202 수락 후 무효 파일을 비동기 단계에서 조용히 폐기(에러 통보 부재) (과거 V2 증거, 이번 미수행)</t>
+          <t>"not_a_valid_url_링크" 같은 비-URL 문자열이 그대로 저장됨</t>
         </is>
       </c>
       <c r="H19" s="52" t="inlineStr">
@@ -2127,42 +2150,43 @@
       </c>
       <c r="J19" s="52" t="inlineStr">
         <is>
-          <t>A-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1" s="47">
+          <t>A-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1" s="47">
       <c r="A20" s="52" t="n">
         <v>17</v>
       </c>
       <c r="B20" s="52" t="inlineStr">
         <is>
-          <t>업로드</t>
+          <t>입력검증</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
         <is>
-          <t>업로드 정책</t>
+          <t>형식 검증</t>
         </is>
       </c>
       <c r="D20" s="52" t="inlineStr">
         <is>
-          <t>gif 처리 불일치</t>
+          <t>이메일</t>
         </is>
       </c>
       <c r="E20" s="53" t="inlineStr">
         <is>
-          <t>1. gif 업로드 후 게이트·비동기 결과 확인</t>
+          <t>[동등분할]
+1. 회사 수정에서 이메일에 @ 없는 문자열 입력·저장</t>
         </is>
       </c>
       <c r="F20" s="53" t="inlineStr">
         <is>
-          <t>지원/미지원 정책 일관</t>
+          <t>이메일 형식 검증·거부</t>
         </is>
       </c>
       <c r="G20" s="53" t="inlineStr">
         <is>
-          <t>gif가 게이트에서 202 수락되나 비동기 단계에서 거부(게이트-처리 불일치). 게이트 통과까지만 확인</t>
+          <t>@ 없는 'invalidemail'이 200으로 저장됨(형식 검증 부재). 테스트 후 원복 완료</t>
         </is>
       </c>
       <c r="H20" s="52" t="inlineStr">
@@ -2177,42 +2201,43 @@
       </c>
       <c r="J20" s="52" t="inlineStr">
         <is>
-          <t>A-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1" s="47">
+          <t>E-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1" s="47">
       <c r="A21" s="52" t="n">
         <v>18</v>
       </c>
       <c r="B21" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>입력검증</t>
         </is>
       </c>
       <c r="C21" s="52" t="inlineStr">
         <is>
-          <t>입력검증</t>
+          <t>경계값</t>
         </is>
       </c>
       <c r="D21" s="52" t="inlineStr">
         <is>
-          <t>URL 형식 검증</t>
+          <t>페이지</t>
         </is>
       </c>
       <c r="E21" s="53" t="inlineStr">
         <is>
-          <t>1. 스페이스 홍보링크(website)에 URL 아닌 문자열 입력·저장</t>
+          <t>[경계값]
+1. page=-1 / page=0 / page=abc로 목록 조회</t>
         </is>
       </c>
       <c r="F21" s="53" t="inlineStr">
         <is>
-          <t>URL 형식 검증·거부</t>
+          <t>잘못된 페이지는 400 검증</t>
         </is>
       </c>
       <c r="G21" s="53" t="inlineStr">
         <is>
-          <t>"not_a_valid_url_링크" 같은 비-URL 문자열이 그대로 저장됨</t>
+          <t>page=-1 → code999, page=0 경계 모호(page=abc는 400 정상). 음수/경계 검증 미흡</t>
         </is>
       </c>
       <c r="H21" s="52" t="inlineStr">
@@ -2227,11 +2252,11 @@
       </c>
       <c r="J21" s="52" t="inlineStr">
         <is>
-          <t>A-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1" s="47">
+          <t>A-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="66" customHeight="1" s="47">
       <c r="A22" s="52" t="n">
         <v>19</v>
       </c>
@@ -2242,7 +2267,7 @@
       </c>
       <c r="C22" s="52" t="inlineStr">
         <is>
-          <t>기본값 처리</t>
+          <t>기본값</t>
         </is>
       </c>
       <c r="D22" s="52" t="inlineStr">
@@ -2252,7 +2277,8 @@
       </c>
       <c r="E22" s="53" t="inlineStr">
         <is>
-          <t>1. welcomeMessage 미입력 스페이스의 저장값 확인</t>
+          <t>[오류주입]
+1. welcomeMessage 미입력 스페이스의 저장값 확인</t>
         </is>
       </c>
       <c r="F22" s="53" t="inlineStr">
@@ -2262,7 +2288,7 @@
       </c>
       <c r="G22" s="53" t="inlineStr">
         <is>
-          <t>리터럴 문자열 "undefined"가 영속화(스페이스 3개 전부). 프론트에서 JS undefined가 문자열로 강제변환 저장 추정</t>
+          <t>리터럴 문자열 "undefined"가 영속화(스페이스 3개 전부). 프론트 undefined→문자열 강제변환 저장 추정</t>
         </is>
       </c>
       <c r="H22" s="52" t="inlineStr">
@@ -2281,38 +2307,39 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1" s="47">
+    <row r="23" ht="66" customHeight="1" s="47">
       <c r="A23" s="52" t="n">
         <v>20</v>
       </c>
       <c r="B23" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C23" s="52" t="inlineStr">
         <is>
-          <t>입력검증</t>
+          <t>정보노출</t>
         </is>
       </c>
       <c r="D23" s="52" t="inlineStr">
         <is>
-          <t>페이지 경계값</t>
+          <t>썸네일 노출</t>
         </is>
       </c>
       <c r="E23" s="53" t="inlineStr">
         <is>
-          <t>1. page=-1 / page=0 / page=abc로 목록 조회</t>
+          <t>[보안 테스트]
+1. 시크릿탭(비로그인)에서 미게시 스페이스 썸네일 URL 직접 열기</t>
         </is>
       </c>
       <c r="F23" s="53" t="inlineStr">
         <is>
-          <t>잘못된 페이지는 400 검증</t>
+          <t>미게시 콘텐츠 썸네일은 인증 필요</t>
         </is>
       </c>
       <c r="G23" s="53" t="inlineStr">
         <is>
-          <t>page=-1 → code999, page=0 경계 모호(page=abc는 400 정상). 음수/경계 검증 미흡</t>
+          <t>미게시(토글 OFF) 썸네일(thumbSquare 240×240)이 비로그인으로 로드됨(A-01 확장). 원본 타일은 403 보호</t>
         </is>
       </c>
       <c r="H23" s="52" t="inlineStr">
@@ -2327,42 +2354,43 @@
       </c>
       <c r="J23" s="52" t="inlineStr">
         <is>
-          <t>A-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1" s="47">
+          <t>N-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="66" customHeight="1" s="47">
       <c r="A24" s="52" t="n">
         <v>21</v>
       </c>
       <c r="B24" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C24" s="52" t="inlineStr">
         <is>
-          <t>정보노출</t>
+          <t>보안 설정</t>
         </is>
       </c>
       <c r="D24" s="52" t="inlineStr">
         <is>
-          <t>응답 정보 최소화</t>
+          <t>CORS</t>
         </is>
       </c>
       <c r="E24" s="53" t="inlineStr">
         <is>
-          <t>1. 응답 헤더 및 로그인 오류 메시지 확인</t>
+          <t>[보안 테스트]
+1. API 응답 CORS 헤더 확인</t>
         </is>
       </c>
       <c r="F24" s="53" t="inlineStr">
         <is>
-          <t>내부 스택/정책 최소 노출</t>
+          <t>명시적 오리진 화이트리스트</t>
         </is>
       </c>
       <c r="G24" s="53" t="inlineStr">
         <is>
-          <t>x-powered-by: Express 노출 + 로그인 검증 오류가 비밀번호 정책(6~20자)까지 노출</t>
+          <t>Access-Control-Allow-Origin: *(와일드카드). Credentials 없어 즉각 세션탈취는 완화되나 화이트리스트 권장</t>
         </is>
       </c>
       <c r="H24" s="52" t="inlineStr">
@@ -2377,42 +2405,43 @@
       </c>
       <c r="J24" s="52" t="inlineStr">
         <is>
-          <t>A-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1" s="47">
+          <t>N-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="66" customHeight="1" s="47">
       <c r="A25" s="52" t="n">
         <v>22</v>
       </c>
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C25" s="52" t="inlineStr">
         <is>
-          <t>표기 일관성</t>
+          <t>보안 설정</t>
         </is>
       </c>
       <c r="D25" s="52" t="inlineStr">
         <is>
-          <t>토스트 문구</t>
+          <t>토큰 저장</t>
         </is>
       </c>
       <c r="E25" s="53" t="inlineStr">
         <is>
-          <t>1. 스페이스 등록/삭제, 핫스팟 등록 토스트 비교</t>
+          <t>[보안 테스트]
+1. 로그인 후 localStorage 확인</t>
         </is>
       </c>
       <c r="F25" s="53" t="inlineStr">
         <is>
-          <t>일관된 띄어쓰기 규칙</t>
+          <t>리프레시 토큰 안전 저장(httpOnly 등)</t>
         </is>
       </c>
       <c r="G25" s="53" t="inlineStr">
         <is>
-          <t>스페이스="등록 되었습니다"(띄움) vs 핫스팟="등록되었습니다"(붙임). 토스트 띄어쓰기 규칙 불일치</t>
+          <t>refreshToken localStorage 평문 저장(A-04 확장). 장기 세션 탈취 표면 확대</t>
         </is>
       </c>
       <c r="H25" s="52" t="inlineStr">
@@ -2427,42 +2456,43 @@
       </c>
       <c r="J25" s="52" t="inlineStr">
         <is>
-          <t>E-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1" s="47">
+          <t>N-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="66" customHeight="1" s="47">
       <c r="A26" s="52" t="n">
         <v>23</v>
       </c>
       <c r="B26" s="52" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C26" s="52" t="inlineStr">
         <is>
-          <t>도움말 정합성</t>
+          <t>정보노출</t>
         </is>
       </c>
       <c r="D26" s="52" t="inlineStr">
         <is>
-          <t>핫스팟 종류</t>
+          <t>응답 정보</t>
         </is>
       </c>
       <c r="E26" s="53" t="inlineStr">
         <is>
-          <t>1. 핫스팟 도움말과 실제 우클릭 메뉴 비교</t>
+          <t>[보안 테스트]
+1. 응답 헤더·로그인 오류 메시지 확인</t>
         </is>
       </c>
       <c r="F26" s="53" t="inlineStr">
         <is>
-          <t>도움말 종류 수·명칭 일치</t>
+          <t>내부 스택/정책 최소 노출</t>
         </is>
       </c>
       <c r="G26" s="53" t="inlineStr">
         <is>
-          <t>도움말 4종(정보·이미지·영상·링크) vs 실제 5종(공지사항·이미지·비디오·링크·예약). 개수(예약 누락)·명칭 불일치</t>
+          <t>x-powered-by: Express 노출 + 로그인 오류가 비밀번호 정책(6~20자)까지 노출</t>
         </is>
       </c>
       <c r="H26" s="52" t="inlineStr">
@@ -2477,42 +2507,43 @@
       </c>
       <c r="J26" s="52" t="inlineStr">
         <is>
-          <t>E-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1" s="47">
+          <t>A-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="66" customHeight="1" s="47">
       <c r="A27" s="52" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="52" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C27" s="52" t="inlineStr">
         <is>
-          <t>업로드 안내</t>
+          <t>정보노출</t>
         </is>
       </c>
       <c r="D27" s="52" t="inlineStr">
         <is>
-          <t>규격 안내</t>
+          <t>파일명 노출</t>
         </is>
       </c>
       <c r="E27" s="53" t="inlineStr">
         <is>
-          <t>1. 개발사 제공 파노라마 업로드 시도</t>
+          <t>[탐색적]
+1. 뷰어/에디터 헤더·탭 제목 확인</t>
         </is>
       </c>
       <c r="F27" s="53" t="inlineStr">
         <is>
-          <t>업로드 성공 또는 권장 규격 안내</t>
+          <t>내부 식별자만 표기</t>
         </is>
       </c>
       <c r="G27" s="53" t="inlineStr">
         <is>
-          <t>제공 파노라마 업로드가 막히고 권장 규격 안내도 없음(원인 파악 불가)</t>
+          <t>헤더·탭에 원본 파일명(예: X3_F-1(2).jpg) 노출 → 촬영장비·세트·순서 유추 프라이버시(A-01 교차)</t>
         </is>
       </c>
       <c r="H27" s="52" t="inlineStr">
@@ -2527,11 +2558,11 @@
       </c>
       <c r="J27" s="52" t="inlineStr">
         <is>
-          <t>E-004</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1" s="47">
+          <t>E-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="66" customHeight="1" s="47">
       <c r="A28" s="52" t="n">
         <v>25</v>
       </c>
@@ -2542,27 +2573,28 @@
       </c>
       <c r="C28" s="52" t="inlineStr">
         <is>
-          <t>자동 명명</t>
+          <t>표기 일관성</t>
         </is>
       </c>
       <c r="D28" s="52" t="inlineStr">
         <is>
-          <t>카테고리 규칙</t>
+          <t>토스트 문구</t>
         </is>
       </c>
       <c r="E28" s="53" t="inlineStr">
         <is>
-          <t>1. F/H 스페이스의 자동생성 카테고리명 확인</t>
+          <t>[탐색적]
+1. 스페이스 등록/삭제, 핫스팟 등록 토스트 비교</t>
         </is>
       </c>
       <c r="F28" s="53" t="inlineStr">
         <is>
-          <t>일관된 자동명명 규칙</t>
+          <t>일관된 띄어쓰기 규칙</t>
         </is>
       </c>
       <c r="G28" s="53" t="inlineStr">
         <is>
-          <t>F스페이스=파일 접두사, H스페이스=스페이스명으로 자동명명 규칙 불일치</t>
+          <t>스페이스="등록 되었습니다"(띄움) vs 핫스팟="등록되었습니다"(붙임). 토스트 띄어쓰기 규칙 불일치</t>
         </is>
       </c>
       <c r="H28" s="52" t="inlineStr">
@@ -2577,11 +2609,11 @@
       </c>
       <c r="J28" s="52" t="inlineStr">
         <is>
-          <t>E-005</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1" s="47">
+          <t>E-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="66" customHeight="1" s="47">
       <c r="A29" s="52" t="n">
         <v>26</v>
       </c>
@@ -2592,27 +2624,28 @@
       </c>
       <c r="C29" s="52" t="inlineStr">
         <is>
-          <t>안정성</t>
+          <t>도움말 정합성</t>
         </is>
       </c>
       <c r="D29" s="52" t="inlineStr">
         <is>
-          <t>배치 렌더 크래시</t>
+          <t>핫스팟 종류</t>
         </is>
       </c>
       <c r="E29" s="53" t="inlineStr">
         <is>
-          <t>1. 배치 업로드 반복 수행</t>
+          <t>[탐색적]
+1. 핫스팟 도움말과 실제 우클릭 메뉴 비교</t>
         </is>
       </c>
       <c r="F29" s="53" t="inlineStr">
         <is>
-          <t>정상 렌더</t>
+          <t>도움말 종류 수·명칭 일치</t>
         </is>
       </c>
       <c r="G29" s="53" t="inlineStr">
         <is>
-          <t>초기 1회 white screen 크래시 목격했으나 이후 33회+ 재시도에도 미재현 → 심각에서 경미로 하향(간헐·재현불가)</t>
+          <t>도움말 4종(정보·이미지·영상·링크) vs 실제 5종(공지사항·이미지·비디오·링크·예약). 개수·명칭 불일치</t>
         </is>
       </c>
       <c r="H29" s="52" t="inlineStr">
@@ -2627,11 +2660,11 @@
       </c>
       <c r="J29" s="52" t="inlineStr">
         <is>
-          <t>E-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1" s="47">
+          <t>E-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="66" customHeight="1" s="47">
       <c r="A30" s="52" t="n">
         <v>27</v>
       </c>
@@ -2642,27 +2675,28 @@
       </c>
       <c r="C30" s="52" t="inlineStr">
         <is>
-          <t>잔여물 처리</t>
+          <t>업로드 안내</t>
         </is>
       </c>
       <c r="D30" s="52" t="inlineStr">
         <is>
-          <t>유령 카테고리</t>
+          <t>규격 안내</t>
         </is>
       </c>
       <c r="E30" s="53" t="inlineStr">
         <is>
-          <t>1. 배치 업로드 실패 후 카테고리 목록 확인</t>
+          <t>[탐색적]
+1. 개발사 제공 파노라마 업로드 시도</t>
         </is>
       </c>
       <c r="F30" s="53" t="inlineStr">
         <is>
-          <t>실패 시 잔여물 없음</t>
+          <t>업로드 성공 또는 권장 규격 안내</t>
         </is>
       </c>
       <c r="G30" s="53" t="inlineStr">
         <is>
-          <t>배치 실패 시 씬 없는 빈 유령 카테고리가 생성·잔존(E-018 동반)</t>
+          <t>제공 파노라마 업로드가 막히고 권장 규격 안내도 없음</t>
         </is>
       </c>
       <c r="H30" s="52" t="inlineStr">
@@ -2677,11 +2711,11 @@
       </c>
       <c r="J30" s="52" t="inlineStr">
         <is>
-          <t>E-011</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1" s="47">
+          <t>E-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="66" customHeight="1" s="47">
       <c r="A31" s="52" t="n">
         <v>28</v>
       </c>
@@ -2692,27 +2726,28 @@
       </c>
       <c r="C31" s="52" t="inlineStr">
         <is>
-          <t>입력 검증 안내</t>
+          <t>자동 명명</t>
         </is>
       </c>
       <c r="D31" s="52" t="inlineStr">
         <is>
-          <t>예약 핫스팟</t>
+          <t>카테고리 규칙</t>
         </is>
       </c>
       <c r="E31" s="53" t="inlineStr">
         <is>
-          <t>1. 예약 핫스팟에서 구역 미선택 상태로 저장 클릭</t>
+          <t>[탐색적]
+1. F/H 스페이스의 자동생성 카테고리명 확인</t>
         </is>
       </c>
       <c r="F31" s="53" t="inlineStr">
         <is>
-          <t>필수값 검증·안내</t>
+          <t>일관된 자동명명 규칙</t>
         </is>
       </c>
       <c r="G31" s="53" t="inlineStr">
         <is>
-          <t>무반응(에러·모달닫힘·저장 전부 없음). 사용자는 저장 실패 이유를 알 수 없음. 단독세션 재검증에서도 재현</t>
+          <t>F스페이스=파일 접두사, H스페이스=스페이스명으로 자동명명 규칙 불일치</t>
         </is>
       </c>
       <c r="H31" s="52" t="inlineStr">
@@ -2727,42 +2762,43 @@
       </c>
       <c r="J31" s="52" t="inlineStr">
         <is>
-          <t>E-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1" s="47">
+          <t>E-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="66" customHeight="1" s="47">
       <c r="A32" s="52" t="n">
         <v>29</v>
       </c>
       <c r="B32" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>정보노출</t>
+          <t>입력 검증 안내</t>
         </is>
       </c>
       <c r="D32" s="52" t="inlineStr">
         <is>
-          <t>파일명 노출</t>
+          <t>예약 핫스팟</t>
         </is>
       </c>
       <c r="E32" s="53" t="inlineStr">
         <is>
-          <t>1. 뷰어/에디터 헤더·탭 제목 확인</t>
+          <t>[결정표]
+1. 예약 핫스팟에서 구역 미선택 상태로 저장 클릭</t>
         </is>
       </c>
       <c r="F32" s="53" t="inlineStr">
         <is>
-          <t>내부 식별자만 표기</t>
+          <t>필수값 검증·안내</t>
         </is>
       </c>
       <c r="G32" s="53" t="inlineStr">
         <is>
-          <t>헤더·탭에 원본 업로드 파일명(예: X3_F-1(2).jpg) 노출 → 촬영장비·세트·순서 유추 프라이버시(A-01 응답서 교차확인)</t>
+          <t>무반응(에러·모달닫힘·저장 전부 없음). 저장 실패 이유를 알 수 없음. 단독세션 재검증에서도 재현</t>
         </is>
       </c>
       <c r="H32" s="52" t="inlineStr">
@@ -2777,11 +2813,11 @@
       </c>
       <c r="J32" s="52" t="inlineStr">
         <is>
-          <t>E-014</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1" s="47">
+          <t>E-013</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="66" customHeight="1" s="47">
       <c r="A33" s="52" t="n">
         <v>30</v>
       </c>
@@ -2792,27 +2828,28 @@
       </c>
       <c r="C33" s="52" t="inlineStr">
         <is>
-          <t>견고성</t>
+          <t>잔여물 처리</t>
         </is>
       </c>
       <c r="D33" s="52" t="inlineStr">
         <is>
-          <t>콘솔 에러</t>
+          <t>유령 카테고리</t>
         </is>
       </c>
       <c r="E33" s="53" t="inlineStr">
         <is>
-          <t>1. 빈 에디터/씬 렌더 시 콘솔 확인</t>
+          <t>[상태전이]
+1. 배치 업로드 실패 후 카테고리 목록 확인</t>
         </is>
       </c>
       <c r="F33" s="53" t="inlineStr">
         <is>
-          <t>콘솔 에러 없음</t>
+          <t>실패 시 잔여물 없음</t>
         </is>
       </c>
       <c r="G33" s="53" t="inlineStr">
         <is>
-          <t>getVisibleChildId에서 'Cannot read properties of null (reading children/classList)' TypeError 반복 발생</t>
+          <t>배치 실패 시 씬 없는 빈 유령 카테고리가 생성·잔존(E-018 동반)</t>
         </is>
       </c>
       <c r="H33" s="52" t="inlineStr">
@@ -2827,11 +2864,11 @@
       </c>
       <c r="J33" s="52" t="inlineStr">
         <is>
-          <t>E-015</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1" s="47">
+          <t>E-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="66" customHeight="1" s="47">
       <c r="A34" s="52" t="n">
         <v>31</v>
       </c>
@@ -2842,27 +2879,28 @@
       </c>
       <c r="C34" s="52" t="inlineStr">
         <is>
-          <t>렌더 지연</t>
+          <t>견고성</t>
         </is>
       </c>
       <c r="D34" s="52" t="inlineStr">
         <is>
-          <t>대표 씬 삭제</t>
+          <t>콘솔 에러</t>
         </is>
       </c>
       <c r="E34" s="53" t="inlineStr">
         <is>
-          <t>1. 대표 씬 삭제 후 다음 씬 진입</t>
+          <t>[탐색적]
+1. 빈 에디터/씬 렌더 시 콘솔 확인</t>
         </is>
       </c>
       <c r="F34" s="53" t="inlineStr">
         <is>
-          <t>즉시 정상 렌더</t>
+          <t>콘솔 에러 없음</t>
         </is>
       </c>
       <c r="G34" s="53" t="inlineStr">
         <is>
-          <t>삭제 직후 다음 씬 검은화면, 상호작용 시 복구(렌더 지연·로딩 표시 부재)</t>
+          <t>getVisibleChildId에서 'Cannot read properties of null' TypeError 반복 발생</t>
         </is>
       </c>
       <c r="H34" s="52" t="inlineStr">
@@ -2877,11 +2915,11 @@
       </c>
       <c r="J34" s="52" t="inlineStr">
         <is>
-          <t>E-016</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="60" customHeight="1" s="47">
+          <t>E-015</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="66" customHeight="1" s="47">
       <c r="A35" s="52" t="n">
         <v>32</v>
       </c>
@@ -2892,27 +2930,28 @@
       </c>
       <c r="C35" s="52" t="inlineStr">
         <is>
-          <t>성능</t>
+          <t>렌더 지연</t>
         </is>
       </c>
       <c r="D35" s="52" t="inlineStr">
         <is>
-          <t>목록 로딩</t>
+          <t>대표 씬 삭제</t>
         </is>
       </c>
       <c r="E35" s="53" t="inlineStr">
         <is>
-          <t>1. 회사 목록 로딩 관찰</t>
+          <t>[상태전이]
+1. 대표 씬 삭제 후 다음 씬 진입</t>
         </is>
       </c>
       <c r="F35" s="53" t="inlineStr">
         <is>
-          <t>정상 렌더</t>
+          <t>즉시 정상 렌더</t>
         </is>
       </c>
       <c r="G35" s="53" t="inlineStr">
         <is>
-          <t>회사 목록 로딩 중 렌더러 프리즈 2회(수초 후 복구)</t>
+          <t>삭제 직후 다음 씬 검은화면, 상호작용 시 복구(렌더 지연·로딩표시 부재)</t>
         </is>
       </c>
       <c r="H35" s="52" t="inlineStr">
@@ -2927,42 +2966,43 @@
       </c>
       <c r="J35" s="52" t="inlineStr">
         <is>
-          <t>E-017</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1" s="47">
+          <t>E-016</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="66" customHeight="1" s="47">
       <c r="A36" s="52" t="n">
         <v>33</v>
       </c>
       <c r="B36" s="52" t="inlineStr">
         <is>
-          <t>업로드</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
         <is>
-          <t>업로드 정책</t>
+          <t>성능</t>
         </is>
       </c>
       <c r="D36" s="52" t="inlineStr">
         <is>
-          <t>accept 불일치</t>
+          <t>목록 로딩</t>
         </is>
       </c>
       <c r="E36" s="53" t="inlineStr">
         <is>
-          <t>1. 업로드 input accept 값과 실제 처리 포맷 비교</t>
+          <t>[탐색적]
+1. 회사 목록 로딩 관찰</t>
         </is>
       </c>
       <c r="F36" s="53" t="inlineStr">
         <is>
-          <t>accept와 실제 처리 정책 일치</t>
+          <t>정상 렌더</t>
         </is>
       </c>
       <c r="G36" s="53" t="inlineStr">
         <is>
-          <t>accept="image/*"인데 실제는 JPEG/PNG만 처리(webp 거부, gif는 게이트 통과 후 거부). affordance-처리 정책 불일치</t>
+          <t>회사 목록 로딩 중 렌더러 프리즈 2회(수초 후 복구)</t>
         </is>
       </c>
       <c r="H36" s="52" t="inlineStr">
@@ -2977,42 +3017,43 @@
       </c>
       <c r="J36" s="52" t="inlineStr">
         <is>
-          <t>E-020</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1" s="47">
+          <t>E-017</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="66" customHeight="1" s="47">
       <c r="A37" s="52" t="n">
         <v>34</v>
       </c>
       <c r="B37" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="C37" s="52" t="inlineStr">
         <is>
-          <t>입력검증</t>
+          <t>현지화</t>
         </is>
       </c>
       <c r="D37" s="52" t="inlineStr">
         <is>
-          <t>이메일 형식</t>
+          <t>핫스팟 삭제 UI</t>
         </is>
       </c>
       <c r="E37" s="53" t="inlineStr">
         <is>
-          <t>1. 회사 수정에서 이메일에 @ 없는 문자열 입력·저장</t>
+          <t>[탐색적]
+1. 핫스팟 삭제 다이얼로그·토스트 확인</t>
         </is>
       </c>
       <c r="F37" s="53" t="inlineStr">
         <is>
-          <t>이메일 형식 검증·거부</t>
+          <t>앱 전체 한글과 일관</t>
         </is>
       </c>
       <c r="G37" s="53" t="inlineStr">
         <is>
-          <t>@ 없는 'invalidemail'이 200으로 저장됨(형식 검증 부재). 테스트 후 원복 완료</t>
+          <t>핫스팟 삭제만 영문("Delete this hotspot"/"Delete successfully.") → 현지화·표기 일관성 결함</t>
         </is>
       </c>
       <c r="H37" s="52" t="inlineStr">
@@ -3027,11 +3068,11 @@
       </c>
       <c r="J37" s="52" t="inlineStr">
         <is>
-          <t>E-022</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1" s="47">
+          <t>E-023</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="66" customHeight="1" s="47">
       <c r="A38" s="52" t="n">
         <v>35</v>
       </c>
@@ -3042,27 +3083,28 @@
       </c>
       <c r="C38" s="52" t="inlineStr">
         <is>
-          <t>현지화</t>
+          <t>안정성</t>
         </is>
       </c>
       <c r="D38" s="52" t="inlineStr">
         <is>
-          <t>핫스팟 삭제 UI</t>
+          <t>배치 렌더</t>
         </is>
       </c>
       <c r="E38" s="53" t="inlineStr">
         <is>
-          <t>1. 핫스팟 삭제 다이얼로그·토스트 확인</t>
+          <t>[탐색적]
+1. 배치 업로드 반복 수행</t>
         </is>
       </c>
       <c r="F38" s="53" t="inlineStr">
         <is>
-          <t>앱 전체 한글과 일관</t>
+          <t>정상 렌더</t>
         </is>
       </c>
       <c r="G38" s="53" t="inlineStr">
         <is>
-          <t>핫스팟 삭제만 영문("Delete this hotspot"/"Delete successfully.") → 현지화·표기 일관성 결함</t>
+          <t>초기 1회 white screen 크래시 목격, 이후 33회+ 재시도에도 미재현 → 심각에서 경미로 하향(간헐·재현불가)</t>
         </is>
       </c>
       <c r="H38" s="52" t="inlineStr">
@@ -3077,11 +3119,11 @@
       </c>
       <c r="J38" s="52" t="inlineStr">
         <is>
-          <t>E-023</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1" s="47">
+          <t>E-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="66" customHeight="1" s="47">
       <c r="A39" s="52" t="n">
         <v>36</v>
       </c>
@@ -3102,7 +3144,8 @@
       </c>
       <c r="E39" s="53" t="inlineStr">
         <is>
-          <t>1. 스페이스 수정 모달에서 값 변경 없이 취소</t>
+          <t>[상태전이]
+1. 스페이스 수정 모달에서 값 변경 없이 취소</t>
         </is>
       </c>
       <c r="F39" s="53" t="inlineStr">
@@ -3112,7 +3155,7 @@
       </c>
       <c r="G39" s="53" t="inlineStr">
         <is>
-          <t>변경 없이 취소해도 "작성 중인 내용이 삭제됩니다" 경고(dirty-check 부재). 가짜 경고 반복이 진짜 경고를 무력화</t>
+          <t>변경 없이 취소해도 "작성 중 내용 삭제" 경고(dirty-check 부재). 가짜 경고 반복이 진짜 경고를 무력화</t>
         </is>
       </c>
       <c r="H39" s="52" t="inlineStr">
@@ -3131,18 +3174,18 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1" s="47">
+    <row r="40" ht="66" customHeight="1" s="47">
       <c r="A40" s="52" t="n">
         <v>37</v>
       </c>
       <c r="B40" s="52" t="inlineStr">
         <is>
-          <t>인증/인가</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="C40" s="52" t="inlineStr">
         <is>
-          <t>UX·인증</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D40" s="52" t="inlineStr">
@@ -3152,7 +3195,8 @@
       </c>
       <c r="E40" s="53" t="inlineStr">
         <is>
-          <t>1. 로그인 폼 required 확인
+          <t>[탐색적]
+1. 로그인 폼 required 확인
 2. 핫스팟 수정 시도</t>
         </is>
       </c>
@@ -3163,7 +3207,7 @@
       </c>
       <c r="G40" s="53" t="inlineStr">
         <is>
-          <t>로그인 폼 email/password HTML required 부재(서버 400으로 방어됨). 핫스팟 수정 불가(삭제 후 재생성 강제) → 고아 핫스팟 위험</t>
+          <t>로그인 폼 required 부재(서버 400 방어됨). 핫스팟 수정 불가(삭제 후 재생성 강제) → 고아 핫스팟 위험</t>
         </is>
       </c>
       <c r="H40" s="52" t="inlineStr">
@@ -3182,38 +3226,39 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1" s="47">
+    <row r="41" ht="66" customHeight="1" s="47">
       <c r="A41" s="52" t="n">
         <v>38</v>
       </c>
       <c r="B41" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>로그인/인증</t>
         </is>
       </c>
       <c r="C41" s="52" t="inlineStr">
         <is>
-          <t>인가(IDOR)</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="D41" s="52" t="inlineStr">
         <is>
-          <t>수평 권한</t>
+          <t>정상 로그인</t>
         </is>
       </c>
       <c r="E41" s="53" t="inlineStr">
         <is>
-          <t>1. Authorization 토큰으로 미소속 cmpnId(1·2·50·99·150·200·300) 조회</t>
+          <t>[경험기반]
+1. 정상 ID/PW 입력 후 로그인</t>
         </is>
       </c>
       <c r="F41" s="53" t="inlineStr">
         <is>
-          <t>미소속 회사 접근 차단</t>
+          <t>정상 로그인 처리·토큰 발급</t>
         </is>
       </c>
       <c r="G41" s="53" t="inlineStr">
         <is>
-          <t>미소속 전부 code103 차단, 소속(100·101)만 데이터. 인접 ID 차단으로 순차 IDOR 반증</t>
+          <t>정상 로그인 성공, accessToken/refreshToken 발급 확인</t>
         </is>
       </c>
       <c r="H41" s="52" t="inlineStr">
@@ -3228,39 +3273,39 @@
       </c>
       <c r="J41" s="52" t="inlineStr"/>
     </row>
-    <row r="42" ht="60" customHeight="1" s="47">
+    <row r="42" ht="66" customHeight="1" s="47">
       <c r="A42" s="52" t="n">
         <v>39</v>
       </c>
       <c r="B42" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>로그인/인증</t>
         </is>
       </c>
       <c r="C42" s="52" t="inlineStr">
         <is>
-          <t>인증</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="D42" s="52" t="inlineStr">
         <is>
-          <t>비인증·로그아웃</t>
+          <t>세션 종료</t>
         </is>
       </c>
       <c r="E42" s="53" t="inlineStr">
         <is>
-          <t>1. 무토큰 API 호출
-2. 로그아웃 후 동일 토큰 재사용</t>
+          <t>[상태전이]
+1. 로그아웃 후 동일 토큰으로 API 재호출</t>
         </is>
       </c>
       <c r="F42" s="53" t="inlineStr">
         <is>
-          <t>비인증 401 + 로그아웃 시 토큰 무효화</t>
+          <t>로그아웃 시 토큰 무효화</t>
         </is>
       </c>
       <c r="G42" s="53" t="inlineStr">
         <is>
-          <t>무토큰 → 401 "token is not valid". 로그아웃 후 동일 토큰 401(서버측 무효화). 토큰 opaque(JWT 아님)</t>
+          <t>로그아웃 후 동일 토큰 401(서버측 무효화). 토큰 opaque(JWT 아님)</t>
         </is>
       </c>
       <c r="H42" s="52" t="inlineStr">
@@ -3275,38 +3320,39 @@
       </c>
       <c r="J42" s="52" t="inlineStr"/>
     </row>
-    <row r="43" ht="60" customHeight="1" s="47">
+    <row r="43" ht="66" customHeight="1" s="47">
       <c r="A43" s="52" t="n">
         <v>40</v>
       </c>
       <c r="B43" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C43" s="52" t="inlineStr">
         <is>
-          <t>주입</t>
+          <t>인가(IDOR)</t>
         </is>
       </c>
       <c r="D43" s="52" t="inlineStr">
         <is>
-          <t>SQL/NoSQL</t>
+          <t>수평 권한</t>
         </is>
       </c>
       <c r="E43" s="53" t="inlineStr">
         <is>
-          <t>1. ' OR 1=1, {$ne:null}, 배열/객체 주입 시도</t>
+          <t>[경계값·부정]
+1. Authorization 토큰으로 미소속 cmpnId(1·2·50·99·150·200·300) 조회</t>
         </is>
       </c>
       <c r="F43" s="53" t="inlineStr">
         <is>
-          <t>주입 방어</t>
+          <t>미소속 회사 접근 차단</t>
         </is>
       </c>
       <c r="G43" s="53" t="inlineStr">
         <is>
-          <t>SQL/NoSQL 페이로드 방어(파라미터 검증), 타입 혼동(배열/객체) → 400</t>
+          <t>미소속 전부 code103 차단, 소속(100·101)만 데이터. 인접 ID 차단으로 순차 IDOR 반증</t>
         </is>
       </c>
       <c r="H43" s="52" t="inlineStr">
@@ -3321,38 +3367,39 @@
       </c>
       <c r="J43" s="52" t="inlineStr"/>
     </row>
-    <row r="44" ht="60" customHeight="1" s="47">
+    <row r="44" ht="66" customHeight="1" s="47">
       <c r="A44" s="52" t="n">
         <v>41</v>
       </c>
       <c r="B44" s="52" t="inlineStr">
         <is>
-          <t>업로드</t>
+          <t>보안(취약점)</t>
         </is>
       </c>
       <c r="C44" s="52" t="inlineStr">
         <is>
-          <t>업로드 검증</t>
+          <t>주입</t>
         </is>
       </c>
       <c r="D44" s="52" t="inlineStr">
         <is>
-          <t>최종 거부</t>
+          <t>SQL/NoSQL</t>
         </is>
       </c>
       <c r="E44" s="53" t="inlineStr">
         <is>
-          <t>1. 0바이트·손상·텍스트위장·SVG·path traversal 파일명 업로드</t>
+          <t>[오류주입]
+1. ' OR 1=1, {$ne:null}, 배열/객체 주입 시도</t>
         </is>
       </c>
       <c r="F44" s="53" t="inlineStr">
         <is>
-          <t>무효/위험 파일 최종 거부</t>
+          <t>주입 방어</t>
         </is>
       </c>
       <c r="G44" s="53" t="inlineStr">
         <is>
-          <t>나쁜 파일(0바이트·손상·webp·bmp) 최종 거부, SVG 거부, path traversal 파일명은 basename만 사용, 타일 본체 스토리지 비인증 403</t>
+          <t>SQL/NoSQL 페이로드 방어(파라미터 검증), 타입 혼동(배열/객체) → 400</t>
         </is>
       </c>
       <c r="H44" s="52" t="inlineStr">
@@ -3367,38 +3414,39 @@
       </c>
       <c r="J44" s="52" t="inlineStr"/>
     </row>
-    <row r="45" ht="60" customHeight="1" s="47">
+    <row r="45" ht="66" customHeight="1" s="47">
       <c r="A45" s="52" t="n">
         <v>42</v>
       </c>
       <c r="B45" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>입력검증</t>
         </is>
       </c>
       <c r="C45" s="52" t="inlineStr">
         <is>
-          <t>정보노출</t>
+          <t>서버측 검증</t>
         </is>
       </c>
       <c r="D45" s="52" t="inlineStr">
         <is>
-          <t>민감정보 비노출</t>
+          <t>생성/경계</t>
         </is>
       </c>
       <c r="E45" s="53" t="inlineStr">
         <is>
-          <t>1. 소스맵·.env 접근, 500 응답 확인</t>
+          <t>[동등분할·경계값]
+1. 빈값/형식오류/좌표·수치/회사명 길이 초과 입력</t>
         </is>
       </c>
       <c r="F45" s="53" t="inlineStr">
         <is>
-          <t>민감 정보 비노출</t>
+          <t>서버측 검증(400)</t>
         </is>
       </c>
       <c r="G45" s="53" t="inlineStr">
         <is>
-          <t>소스맵·.env → 404, 500 응답 스택 미노출</t>
+          <t>POST /content 생성 검증(400), 좌표/수치 검증(400), 회사명 길이 상한(400), 로그인 빈값 → 400</t>
         </is>
       </c>
       <c r="H45" s="52" t="inlineStr">
@@ -3413,38 +3461,39 @@
       </c>
       <c r="J45" s="52" t="inlineStr"/>
     </row>
-    <row r="46" ht="60" customHeight="1" s="47">
+    <row r="46" ht="66" customHeight="1" s="47">
       <c r="A46" s="52" t="n">
         <v>43</v>
       </c>
       <c r="B46" s="52" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>업로드</t>
         </is>
       </c>
       <c r="C46" s="52" t="inlineStr">
         <is>
-          <t>입력검증</t>
+          <t>업로드 검증</t>
         </is>
       </c>
       <c r="D46" s="52" t="inlineStr">
         <is>
-          <t>서버측 검증</t>
+          <t>위험파일 거부</t>
         </is>
       </c>
       <c r="E46" s="53" t="inlineStr">
         <is>
-          <t>1. 빈값/형식오류/좌표·수치/회사명 길이 초과 입력</t>
+          <t>[오류주입]
+1. SVG·path traversal 파일명·손상 파일 업로드</t>
         </is>
       </c>
       <c r="F46" s="53" t="inlineStr">
         <is>
-          <t>서버측 검증(400)</t>
+          <t>위험 파일 거부</t>
         </is>
       </c>
       <c r="G46" s="53" t="inlineStr">
         <is>
-          <t>POST /content 생성 검증(400), 좌표/수치 검증(400), 회사명 길이 상한(400), 로그인 빈값 → 400 class-validator</t>
+          <t>SVG 거부, path traversal 파일명은 basename만 사용, 나쁜 파일 최종 거부, 타일 본체 스토리지 비인증 403</t>
         </is>
       </c>
       <c r="H46" s="52" t="inlineStr">
@@ -3458,6 +3507,242 @@
         </is>
       </c>
       <c r="J46" s="52" t="inlineStr"/>
+    </row>
+    <row r="47" ht="66" customHeight="1" s="47">
+      <c r="A47" s="52" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="52" t="inlineStr">
+        <is>
+          <t>스페이스/VT</t>
+        </is>
+      </c>
+      <c r="C47" s="52" t="inlineStr">
+        <is>
+          <t>스페이스 관리</t>
+        </is>
+      </c>
+      <c r="D47" s="52" t="inlineStr">
+        <is>
+          <t>생성·삭제</t>
+        </is>
+      </c>
+      <c r="E47" s="53" t="inlineStr">
+        <is>
+          <t>[상태전이]
+1. 스페이스 생성 후 삭제
+2. 목록·토스트 확인</t>
+        </is>
+      </c>
+      <c r="F47" s="53" t="inlineStr">
+        <is>
+          <t>생성·삭제 정상 반영</t>
+        </is>
+      </c>
+      <c r="G47" s="53" t="inlineStr">
+        <is>
+          <t>스페이스 생성·삭제 정상 동작, 삭제 토스트 정상(잔존 없음 확인)</t>
+        </is>
+      </c>
+      <c r="H47" s="52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I47" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="52" t="inlineStr"/>
+    </row>
+    <row r="48" ht="66" customHeight="1" s="47">
+      <c r="A48" s="52" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="52" t="inlineStr">
+        <is>
+          <t>스페이스/VT</t>
+        </is>
+      </c>
+      <c r="C48" s="52" t="inlineStr">
+        <is>
+          <t>공유</t>
+        </is>
+      </c>
+      <c r="D48" s="52" t="inlineStr">
+        <is>
+          <t>링크 복사</t>
+        </is>
+      </c>
+      <c r="E48" s="53" t="inlineStr">
+        <is>
+          <t>[경험기반]
+1. 공유 버튼 클릭</t>
+        </is>
+      </c>
+      <c r="F48" s="53" t="inlineStr">
+        <is>
+          <t>공유 링크 복사·안내</t>
+        </is>
+      </c>
+      <c r="G48" s="53" t="inlineStr">
+        <is>
+          <t>"주소가 복사되었습니다" 토스트 정상 표시(정상 동작)</t>
+        </is>
+      </c>
+      <c r="H48" s="52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I48" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="52" t="inlineStr"/>
+    </row>
+    <row r="49" ht="66" customHeight="1" s="47">
+      <c r="A49" s="52" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="52" t="inlineStr">
+        <is>
+          <t>핫스팟</t>
+        </is>
+      </c>
+      <c r="C49" s="52" t="inlineStr">
+        <is>
+          <t>핫스팟 생성</t>
+        </is>
+      </c>
+      <c r="D49" s="52" t="inlineStr">
+        <is>
+          <t>4종 생성</t>
+        </is>
+      </c>
+      <c r="E49" s="53" t="inlineStr">
+        <is>
+          <t>[탐색적]
+1. 공지·이미지·비디오·링크 핫스팟 각각 생성</t>
+        </is>
+      </c>
+      <c r="F49" s="53" t="inlineStr">
+        <is>
+          <t>각 유형 정상 생성</t>
+        </is>
+      </c>
+      <c r="G49" s="53" t="inlineStr">
+        <is>
+          <t>공지·이미지·비디오·링크 핫스팟 생성 정상 동작(이미지 핫스팟 업로드 안내 20MB·jpg/png/gif 명확)</t>
+        </is>
+      </c>
+      <c r="H49" s="52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I49" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="52" t="inlineStr"/>
+    </row>
+    <row r="50" ht="66" customHeight="1" s="47">
+      <c r="A50" s="52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="52" t="inlineStr">
+        <is>
+          <t>회사</t>
+        </is>
+      </c>
+      <c r="C50" s="52" t="inlineStr">
+        <is>
+          <t>회사 관리</t>
+        </is>
+      </c>
+      <c r="D50" s="52" t="inlineStr">
+        <is>
+          <t>정보 수정</t>
+        </is>
+      </c>
+      <c r="E50" s="53" t="inlineStr">
+        <is>
+          <t>[상태전이]
+1. 회사 정보 수정 후 저장</t>
+        </is>
+      </c>
+      <c r="F50" s="53" t="inlineStr">
+        <is>
+          <t>수정 정상 반영</t>
+        </is>
+      </c>
+      <c r="G50" s="53" t="inlineStr">
+        <is>
+          <t>회사 정보 수정 정상 반영("수정이 완료 되었습니다"). 이메일 형식검증만 결함(E-022)</t>
+        </is>
+      </c>
+      <c r="H50" s="52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I50" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="52" t="inlineStr"/>
+    </row>
+    <row r="51" ht="66" customHeight="1" s="47">
+      <c r="A51" s="52" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="52" t="inlineStr">
+        <is>
+          <t>스페이스/VT</t>
+        </is>
+      </c>
+      <c r="C51" s="52" t="inlineStr">
+        <is>
+          <t>노출 제어</t>
+        </is>
+      </c>
+      <c r="D51" s="52" t="inlineStr">
+        <is>
+          <t>active 토글</t>
+        </is>
+      </c>
+      <c r="E51" s="53" t="inlineStr">
+        <is>
+          <t>[상태전이]
+1. 스페이스 active 토글 ON/OFF</t>
+        </is>
+      </c>
+      <c r="F51" s="53" t="inlineStr">
+        <is>
+          <t>게시 상태 반영</t>
+        </is>
+      </c>
+      <c r="G51" s="53" t="inlineStr">
+        <is>
+          <t>active 토글 동작 확인(테스트 스페이스는 비노출 OFF 유지)</t>
+        </is>
+      </c>
+      <c r="H51" s="52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I51" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="52" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3477,7 +3762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.6640625" customWidth="1" style="19" min="1" max="1"/>
@@ -3511,12 +3796,12 @@
       </c>
       <c r="B2" s="52" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>E-018</t>
         </is>
       </c>
       <c r="C2" s="53" t="inlineStr">
         <is>
-          <t>recon/01_home.png</t>
+          <t>recon/40_after_uploads.png</t>
         </is>
       </c>
     </row>
@@ -3526,12 +3811,12 @@
       </c>
       <c r="B3" s="52" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C3" s="53" t="inlineStr">
         <is>
-          <t>recon/03_login.png</t>
+          <t>recon/21_company_inside.png</t>
         </is>
       </c>
     </row>
@@ -3541,12 +3826,12 @@
       </c>
       <c r="B4" s="52" t="inlineStr">
         <is>
-          <t>A-11</t>
+          <t>N-3</t>
         </is>
       </c>
       <c r="C4" s="53" t="inlineStr">
         <is>
-          <t>recon/04_empty_login.png</t>
+          <t>recon/N3_thumbnail.png</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3841,12 @@
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t>E-015</t>
+          <t>E-019</t>
         </is>
       </c>
       <c r="C5" s="53" t="inlineStr">
         <is>
-          <t>recon/05_bad_route.png</t>
+          <t>recon/50_async_final.png</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3856,12 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>E-017</t>
+          <t>E-009</t>
         </is>
       </c>
       <c r="C6" s="53" t="inlineStr">
         <is>
-          <t>recon/20_company_list.png</t>
+          <t>recon/51_async_final2.png</t>
         </is>
       </c>
     </row>
@@ -3586,12 +3871,12 @@
       </c>
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>E-009</t>
         </is>
       </c>
       <c r="C7" s="53" t="inlineStr">
         <is>
-          <t>recon/21_company_inside.png</t>
+          <t>recon/v3shots/square.png</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3886,12 @@
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>E-012</t>
+          <t>E-009</t>
         </is>
       </c>
       <c r="C8" s="53" t="inlineStr">
         <is>
-          <t>recon/30_editor.png</t>
+          <t>recon/v3shots/vertical.png</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3901,12 @@
       </c>
       <c r="B9" s="52" t="inlineStr">
         <is>
-          <t>E-018</t>
+          <t>E-019</t>
         </is>
       </c>
       <c r="C9" s="53" t="inlineStr">
         <is>
-          <t>recon/40_after_uploads.png</t>
+          <t>recon/v3shots/normal.png</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3916,12 @@
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>E-019</t>
+          <t>E-012</t>
         </is>
       </c>
       <c r="C10" s="53" t="inlineStr">
         <is>
-          <t>recon/50_async_final.png</t>
+          <t>recon/30_editor.png</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3931,12 @@
       </c>
       <c r="B11" s="52" t="inlineStr">
         <is>
-          <t>E-009</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C11" s="53" t="inlineStr">
         <is>
-          <t>recon/51_async_final2.png</t>
+          <t>recon/03_login.png</t>
         </is>
       </c>
     </row>
@@ -3661,12 +3946,12 @@
       </c>
       <c r="B12" s="52" t="inlineStr">
         <is>
-          <t>E-016</t>
+          <t>A-11</t>
         </is>
       </c>
       <c r="C12" s="53" t="inlineStr">
         <is>
-          <t>recon/60_diag_editor.png</t>
+          <t>recon/04_empty_login.png</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3961,12 @@
       </c>
       <c r="B13" s="52" t="inlineStr">
         <is>
-          <t>E-014</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C13" s="53" t="inlineStr">
         <is>
-          <t>recon/70_aside_editor.png</t>
+          <t>recon/01_home.png</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3976,12 @@
       </c>
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>N-3</t>
+          <t>E-015</t>
         </is>
       </c>
       <c r="C14" s="53" t="inlineStr">
         <is>
-          <t>recon/N3_thumbnail.png</t>
+          <t>recon/05_bad_route.png</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3991,12 @@
       </c>
       <c r="B15" s="52" t="inlineStr">
         <is>
-          <t>E-009</t>
+          <t>E-016</t>
         </is>
       </c>
       <c r="C15" s="53" t="inlineStr">
         <is>
-          <t>recon/v3shots/square.png</t>
+          <t>recon/60_diag_editor.png</t>
         </is>
       </c>
     </row>
@@ -3721,12 +4006,12 @@
       </c>
       <c r="B16" s="52" t="inlineStr">
         <is>
-          <t>E-009</t>
+          <t>E-014</t>
         </is>
       </c>
       <c r="C16" s="53" t="inlineStr">
         <is>
-          <t>recon/v3shots/vertical.png</t>
+          <t>recon/70_aside_editor.png</t>
         </is>
       </c>
     </row>
@@ -3736,12 +4021,42 @@
       </c>
       <c r="B17" s="52" t="inlineStr">
         <is>
-          <t>E-019</t>
+          <t>E-017</t>
         </is>
       </c>
       <c r="C17" s="53" t="inlineStr">
         <is>
-          <t>recon/v3shots/normal.png</t>
+          <t>recon/20_company_list.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="52" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="52" t="inlineStr">
+        <is>
+          <t>로그인 PASS</t>
+        </is>
+      </c>
+      <c r="C18" s="53" t="inlineStr">
+        <is>
+          <t>recon/11_after_login.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="52" t="inlineStr">
+        <is>
+          <t>커버리지</t>
+        </is>
+      </c>
+      <c r="C19" s="53" t="inlineStr">
+        <is>
+          <t>recon/02_main.png</t>
         </is>
       </c>
     </row>

--- a/붙임2. SW제품 테스트 결과보고서(작성본).xlsx
+++ b/붙임2. SW제품 테스트 결과보고서(작성본).xlsx
@@ -561,6 +561,386 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3000375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2619375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3000375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2847975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3000375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2590800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3371850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2457450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2476500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2476500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2743200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -3578,12 +3958,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="13.6640625" customWidth="1" style="9" min="1" max="1"/>
-    <col width="11.6640625" customWidth="1" style="9" min="2" max="2"/>
-    <col width="30.83203125" customWidth="1" style="9" min="3" max="3"/>
+    <col width="9" customWidth="1" style="9" min="1" max="1"/>
+    <col width="12" customWidth="1" style="9" min="2" max="2"/>
+    <col width="92" customWidth="1" style="9" min="3" max="3"/>
     <col width="8.83203125" customWidth="1" style="26" min="4" max="10"/>
     <col width="30.5" customWidth="1" style="26" min="11" max="11"/>
     <col width="8.83203125" customWidth="1" style="26" min="12" max="12"/>
@@ -3607,282 +3987,180 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32.25" customHeight="1" s="28">
-      <c r="A2" s="17" t="n">
+    <row r="2" ht="244.25" customHeight="1" s="28">
+      <c r="A2" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="n"/>
+    </row>
+    <row r="3" ht="214.25" customHeight="1" s="28">
+      <c r="A3" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>E-018</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>recon/40_after_uploads.png</t>
-        </is>
-      </c>
-      <c r="K2" s="26" t="n"/>
-    </row>
-    <row r="3" ht="32.25" customHeight="1" s="28">
-      <c r="A3" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>recon/21_company_inside.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32.25" customHeight="1" s="28">
-      <c r="A4" s="17" t="n">
+      <c r="C3" s="29" t="n"/>
+    </row>
+    <row r="4" ht="244.25" customHeight="1" s="28">
+      <c r="A4" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="n"/>
+    </row>
+    <row r="5" ht="232.25" customHeight="1" s="28">
+      <c r="A5" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="n"/>
+    </row>
+    <row r="6" ht="244.25" customHeight="1" s="28">
+      <c r="A6" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>A-04</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n"/>
+    </row>
+    <row r="7" ht="212" customHeight="1" s="28">
+      <c r="A7" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>E-019</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n"/>
+    </row>
+    <row r="8" ht="233" customHeight="1" s="28">
+      <c r="A8" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>N-2</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="273.5" customHeight="1" s="28">
+      <c r="A9" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>N-3</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>recon/N3_thumbnail.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32.25" customHeight="1" s="28">
-      <c r="A5" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>E-019</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>recon/50_async_final.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1" s="28">
-      <c r="A6" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>E-009</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>recon/51_async_final2.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1" s="28">
-      <c r="A7" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>E-009</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>recon/v3shots/square.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1" s="28">
-      <c r="A8" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>E-009</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>recon/v3shots/vertical.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1" s="28">
-      <c r="A9" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>E-019</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>recon/v3shots/normal.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1" s="28">
-      <c r="A10" s="17" t="n">
+      <c r="C9" s="29" t="n"/>
+    </row>
+    <row r="10" ht="201.5" customHeight="1" s="28">
+      <c r="A10" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>E-012</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>recon/30_editor.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1" s="28">
-      <c r="A11" s="17" t="n">
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>A-05</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n"/>
+    </row>
+    <row r="11" ht="194" customHeight="1" s="28">
+      <c r="A11" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>recon/03_login.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1" s="28">
-      <c r="A12" s="17" t="n">
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>A-08</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="n"/>
+    </row>
+    <row r="12" ht="203" customHeight="1" s="28">
+      <c r="A12" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>A-09</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="n"/>
+    </row>
+    <row r="13" ht="203" customHeight="1" s="28">
+      <c r="A13" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>A-10</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n"/>
+    </row>
+    <row r="14" ht="233" customHeight="1" s="28">
+      <c r="A14" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>A-11</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>recon/04_empty_login.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1" s="28">
-      <c r="A13" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A-04</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>recon/01_home.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1" s="28">
-      <c r="A14" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>E-015</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>recon/05_bad_route.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1" s="28">
-      <c r="A15" s="17" t="n">
+      <c r="C14" s="29" t="n"/>
+    </row>
+    <row r="15" ht="194" customHeight="1" s="28">
+      <c r="A15" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>E-016</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>recon/60_diag_editor.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1" s="28">
-      <c r="A16" s="17" t="n">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>E-020</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="224" customHeight="1" s="28">
+      <c r="A16" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>E-014</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>recon/70_aside_editor.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1" s="28">
-      <c r="A17" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>E-017</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>recon/20_company_list.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1" s="28">
-      <c r="A18" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>로그인 PASS</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>recon/11_after_login.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1" s="28">
-      <c r="A19" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>커버리지</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>recon/02_main.png</t>
-        </is>
-      </c>
-    </row>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>E-022</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1" s="28"/>
+    <row r="18" ht="16" customHeight="1" s="28"/>
+    <row r="19" ht="16" customHeight="1" s="28"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="K2:K10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/붙임2. SW제품 테스트 결과보고서(작성본).xlsx
+++ b/붙임2. SW제품 테스트 결과보고서(작성본).xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="돋움"/>
       <charset val="129"/>
@@ -152,6 +152,11 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -345,7 +350,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -426,6 +431,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="59">
@@ -565,12 +573,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3000375"/>
+    <ext cx="6286500" cy="3200400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -590,12 +598,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2619375"/>
+    <ext cx="6286500" cy="2790825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -615,12 +623,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3000375"/>
+    <ext cx="6286500" cy="3190875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -640,12 +648,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2847975"/>
+    <ext cx="6286500" cy="3038475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -665,12 +673,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3000375"/>
+    <ext cx="6286500" cy="3190875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -690,12 +698,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2590800"/>
+    <ext cx="6286500" cy="2752725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -715,12 +723,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2857500"/>
+    <ext cx="6286500" cy="2609850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -740,12 +748,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3371850"/>
+    <ext cx="6286500" cy="3467100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -765,12 +773,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2457450"/>
+    <ext cx="6286500" cy="2638425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -790,12 +798,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2362200"/>
+    <ext cx="6286500" cy="2638425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -815,12 +823,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2476500"/>
+    <ext cx="6286500" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -840,12 +848,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2476500"/>
+    <ext cx="6286500" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -865,12 +873,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2857500"/>
+    <ext cx="6286500" cy="3590925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -890,12 +898,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2362200"/>
+    <ext cx="6286500" cy="3467100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -915,12 +923,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2743200"/>
+    <ext cx="6286500" cy="3467100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -928,6 +936,106 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6286500" cy="3467100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6286500" cy="2514600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6286500" cy="2914650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6286500" cy="3467100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3958,36 +4066,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="9" min="1" max="1"/>
-    <col width="12" customWidth="1" style="9" min="2" max="2"/>
-    <col width="92" customWidth="1" style="9" min="3" max="3"/>
-    <col width="8.83203125" customWidth="1" style="26" min="4" max="10"/>
+    <col width="16" customWidth="1" style="9" min="2" max="2"/>
+    <col width="11" customWidth="1" style="9" min="3" max="3"/>
+    <col width="100" customWidth="1" style="26" min="4" max="10"/>
     <col width="30.5" customWidth="1" style="26" min="11" max="11"/>
     <col width="8.83203125" customWidth="1" style="26" min="12" max="12"/>
     <col width="8.83203125" customWidth="1" style="26" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="9">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>이미지 No</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="31" t="inlineStr">
         <is>
           <t>결함 ID</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>증거 유형</t>
+        </is>
+      </c>
+      <c r="D1" s="31" t="inlineStr">
         <is>
           <t>이미지</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="244.25" customHeight="1" s="28">
+    <row r="2" ht="260" customHeight="1" s="28">
       <c r="A2" s="29" t="n">
         <v>1</v>
       </c>
@@ -3996,9 +4109,14 @@
           <t>A-01</t>
         </is>
       </c>
-      <c r="C2" s="29" t="n"/>
-    </row>
-    <row r="3" ht="214.25" customHeight="1" s="28">
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D2" s="29" t="n"/>
+    </row>
+    <row r="3" ht="227.75" customHeight="1" s="28">
       <c r="A3" s="29" t="n">
         <v>2</v>
       </c>
@@ -4007,9 +4125,14 @@
           <t>E-018</t>
         </is>
       </c>
-      <c r="C3" s="29" t="n"/>
-    </row>
-    <row r="4" ht="244.25" customHeight="1" s="28">
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="n"/>
+    </row>
+    <row r="4" ht="259.25" customHeight="1" s="28">
       <c r="A4" s="29" t="n">
         <v>3</v>
       </c>
@@ -4018,9 +4141,14 @@
           <t>A-02</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n"/>
-    </row>
-    <row r="5" ht="232.25" customHeight="1" s="28">
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="n"/>
+    </row>
+    <row r="5" ht="247.25" customHeight="1" s="28">
       <c r="A5" s="29" t="n">
         <v>4</v>
       </c>
@@ -4029,9 +4157,14 @@
           <t>A-03</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n"/>
-    </row>
-    <row r="6" ht="244.25" customHeight="1" s="28">
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="n"/>
+    </row>
+    <row r="6" ht="259.25" customHeight="1" s="28">
       <c r="A6" s="29" t="n">
         <v>5</v>
       </c>
@@ -4040,9 +4173,14 @@
           <t>A-04</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n"/>
-    </row>
-    <row r="7" ht="212" customHeight="1" s="28">
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="n"/>
+    </row>
+    <row r="7" ht="224.75" customHeight="1" s="28">
       <c r="A7" s="29" t="n">
         <v>6</v>
       </c>
@@ -4051,110 +4189,221 @@
           <t>E-019</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n"/>
-    </row>
-    <row r="8" ht="233" customHeight="1" s="28">
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="n"/>
+    </row>
+    <row r="8" ht="213.5" customHeight="1" s="28">
       <c r="A8" s="29" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>N-2</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="n"/>
-    </row>
-    <row r="9" ht="273.5" customHeight="1" s="28">
+          <t>A-05</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="281" customHeight="1" s="28">
       <c r="A9" s="29" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>N-3</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="n"/>
-    </row>
-    <row r="10" ht="201.5" customHeight="1" s="28">
+          <t>A-08</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>실제화면</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n"/>
+    </row>
+    <row r="10" ht="215.75" customHeight="1" s="28">
       <c r="A10" s="29" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>A-05</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="n"/>
-    </row>
-    <row r="11" ht="194" customHeight="1" s="28">
+          <t>A-09</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="n"/>
+    </row>
+    <row r="11" ht="215.75" customHeight="1" s="28">
       <c r="A11" s="29" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>A-08</t>
-        </is>
-      </c>
-      <c r="C11" s="29" t="n"/>
-    </row>
-    <row r="12" ht="203" customHeight="1" s="28">
+          <t>A-10</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n"/>
+    </row>
+    <row r="12" ht="248" customHeight="1" s="28">
       <c r="A12" s="29" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>A-09</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="n"/>
-    </row>
-    <row r="13" ht="203" customHeight="1" s="28">
+          <t>A-11</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="n"/>
+    </row>
+    <row r="13" ht="248" customHeight="1" s="28">
       <c r="A13" s="29" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>A-10</t>
-        </is>
-      </c>
-      <c r="C13" s="29" t="n"/>
-    </row>
-    <row r="14" ht="233" customHeight="1" s="28">
+          <t>N-2</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="n"/>
+    </row>
+    <row r="14" ht="290.75" customHeight="1" s="28">
       <c r="A14" s="29" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>A-11</t>
-        </is>
-      </c>
-      <c r="C14" s="29" t="n"/>
-    </row>
-    <row r="15" ht="194" customHeight="1" s="28">
+          <t>N-3</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>실제화면</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="n"/>
+    </row>
+    <row r="15" ht="281" customHeight="1" s="28">
       <c r="A15" s="29" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>E-020</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="n"/>
-    </row>
-    <row r="16" ht="224" customHeight="1" s="28">
+          <t>E-003 도움말4종</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>실제화면</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="n"/>
+    </row>
+    <row r="16" ht="281" customHeight="1" s="28">
       <c r="A16" s="29" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
+          <t>E-003 메뉴5종</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>실제화면</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="n"/>
+    </row>
+    <row r="17" ht="281" customHeight="1" s="28">
+      <c r="A17" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>E-014</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>실제화면</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="206" customHeight="1" s="28">
+      <c r="A18" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>E-020</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="n"/>
+    </row>
+    <row r="19" ht="237.5" customHeight="1" s="28">
+      <c r="A19" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
           <t>E-022</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n"/>
-    </row>
-    <row r="17" ht="16" customHeight="1" s="28"/>
-    <row r="18" ht="16" customHeight="1" s="28"/>
-    <row r="19" ht="16" customHeight="1" s="28"/>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>실측응답</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="n"/>
+    </row>
+    <row r="20" ht="281" customHeight="1" s="28">
+      <c r="A20" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>E-001</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>실제화면</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="K2:K10"/>

--- a/붙임2. SW제품 테스트 결과보고서(작성본).xlsx
+++ b/붙임2. SW제품 테스트 결과보고서(작성본).xlsx
@@ -3586,7 +3586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="9" min="1" max="1"/>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="C2" s="30" t="inlineStr">
         <is>
-          <t>증적/A-01.png</t>
+          <t>evidence/A-01.png</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="C3" s="30" t="inlineStr">
         <is>
-          <t>증적/E-018.png</t>
+          <t>evidence/E-018.png</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="C4" s="30" t="inlineStr">
         <is>
-          <t>증적/A-02.png</t>
+          <t>evidence/A-02.png</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>증적/A-03.png</t>
+          <t>evidence/A-03.png</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>증적/A-04.png</t>
+          <t>evidence/A-04.png</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>증적/E-009.png</t>
+          <t>evidence/E-009.png</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>증적/E-012.png</t>
+          <t>evidence/E-012.png</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>증적/E-019.png</t>
+          <t>evidence/E-019.png</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>증적/A-05.png</t>
+          <t>evidence/A-05.png</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>증적/A-06.png</t>
+          <t>evidence/A-06.png</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>증적/A-07.png</t>
+          <t>evidence/A-07.png</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>증적/A-08.png</t>
+          <t>evidence/A-08.png</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>증적/A-09.png</t>
+          <t>evidence/A-09.png</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>증적/A-10.png</t>
+          <t>evidence/A-10.png</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>증적/A-11.png</t>
+          <t>evidence/A-11.png</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>증적/N-2.png</t>
+          <t>evidence/N-2.png</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>증적/N-3.png</t>
+          <t>evidence/N-3.png</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>증적/N-4.png</t>
+          <t>evidence/N-4.png</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>증적/N-5.png</t>
+          <t>evidence/N-5.png</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>증적/E-003_도움말.png</t>
+          <t>evidence/E-003_도움말.png</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>증적/E-003_메뉴.png</t>
+          <t>evidence/E-003_메뉴.png</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>증적/E-004.png</t>
+          <t>evidence/E-004.png</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>증적/E-005.png</t>
+          <t>evidence/E-005.png</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>증적/E-011.png</t>
+          <t>evidence/E-011.png</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>증적/E-013.png</t>
+          <t>evidence/E-013.png</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>증적/E-014.png</t>
+          <t>evidence/E-014.png</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>증적/E-015.png</t>
+          <t>evidence/E-015.png</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>증적/E-016.png</t>
+          <t>evidence/E-016.png</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>증적/E-017.png</t>
+          <t>evidence/E-017.png</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>증적/E-020.png</t>
+          <t>evidence/E-020.png</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>증적/E-022.png</t>
+          <t>evidence/E-022.png</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>증적/E-023.png</t>
+          <t>evidence/E-023.png</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>증적/E-001.png</t>
+          <t>evidence/E-001.png</t>
         </is>
       </c>
     </row>
